--- a/diseases/d149/2010-2014.xlsx
+++ b/diseases/d149/2010-2014.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1501,6 +1526,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1646,6 +1676,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1791,6 +1826,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1936,6 +1976,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2084,6 +2129,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2229,6 +2279,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2374,6 +2429,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2519,6 +2579,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2664,6 +2729,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2809,6 +2879,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2954,6 +3029,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3099,6 +3179,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3244,6 +3329,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3392,6 +3482,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3537,6 +3632,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3682,6 +3782,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3827,6 +3932,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3972,6 +4082,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4117,6 +4232,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4262,6 +4382,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4398,6 +4523,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4543,6 +4673,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4691,6 +4826,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4836,6 +4976,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4981,6 +5126,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5126,6 +5276,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5271,6 +5426,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5416,6 +5576,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5561,6 +5726,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5706,6 +5876,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5851,6 +6026,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5999,6 +6179,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6144,6 +6329,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6289,6 +6479,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6434,6 +6629,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6579,6 +6779,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6724,6 +6929,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6869,6 +7079,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7014,6 +7229,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7159,6 +7379,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7307,6 +7532,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7452,6 +7682,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7597,6 +7832,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7742,6 +7982,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7887,6 +8132,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8032,6 +8282,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8177,6 +8432,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8322,6 +8582,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8467,6 +8732,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8615,6 +8885,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8760,6 +9035,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8905,6 +9185,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9050,6 +9335,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9195,6 +9485,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9340,6 +9635,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9485,6 +9785,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9621,6 +9926,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9766,6 +10076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9914,6 +10229,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10059,6 +10379,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10204,6 +10529,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10349,6 +10679,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10494,6 +10829,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10639,6 +10979,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10784,6 +11129,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10920,6 +11270,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11065,6 +11420,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11213,6 +11573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11358,6 +11723,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11503,6 +11873,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11648,6 +12023,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11793,6 +12173,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11938,6 +12323,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12083,6 +12473,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12228,6 +12623,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12373,6 +12773,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12521,6 +12926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12666,6 +13076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12802,6 +13217,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12947,6 +13367,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13092,6 +13517,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13237,6 +13667,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13382,6 +13817,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13518,6 +13958,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13663,6 +14108,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13811,6 +14261,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13956,6 +14411,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14101,6 +14561,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14246,6 +14711,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14391,6 +14861,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14536,6 +15011,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14681,6 +15161,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14817,6 +15302,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14962,6 +15452,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15110,6 +15605,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15255,6 +15755,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15400,6 +15905,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15545,6 +16055,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15681,6 +16196,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15826,6 +16346,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15971,6 +16496,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16107,6 +16637,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16252,6 +16787,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16400,6 +16940,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16545,6 +17090,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16690,6 +17240,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16835,6 +17390,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16980,6 +17540,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17125,6 +17690,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17270,6 +17840,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17406,6 +17981,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17551,6 +18131,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17699,6 +18284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17844,6 +18434,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17989,6 +18584,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18134,6 +18734,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18279,6 +18884,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18424,6 +19034,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18569,6 +19184,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18705,6 +19325,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18850,6 +19475,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18998,6 +19628,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19143,6 +19778,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19288,6 +19928,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19433,6 +20078,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19578,6 +20228,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19723,6 +20378,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19868,6 +20528,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20013,6 +20678,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20158,6 +20828,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20306,6 +20981,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20451,6 +21131,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20596,6 +21281,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20741,6 +21431,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20886,6 +21581,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21031,6 +21731,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21176,6 +21881,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21312,6 +22022,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21457,6 +22172,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21605,6 +22325,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21750,6 +22475,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21895,6 +22625,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22040,6 +22775,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22185,6 +22925,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22330,6 +23075,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22475,6 +23225,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22620,6 +23375,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22765,6 +23525,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22913,6 +23678,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23058,6 +23828,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23203,6 +23978,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23348,6 +24128,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23484,6 +24269,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23629,6 +24419,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23774,6 +24569,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23910,6 +24710,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24055,6 +24860,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24203,6 +25013,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24348,6 +25163,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24493,6 +25313,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24638,6 +25463,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24783,6 +25613,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24928,6 +25763,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25073,6 +25913,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25209,6 +26054,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25354,6 +26204,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25502,6 +26357,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25647,6 +26507,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25792,6 +26657,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25937,6 +26807,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26082,6 +26957,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26227,6 +27107,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26372,6 +27257,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26508,6 +27398,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26653,6 +27548,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26801,6 +27701,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26946,6 +27851,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27091,6 +28001,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27236,6 +28151,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27381,6 +28301,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27526,6 +28451,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27671,6 +28601,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27807,6 +28742,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27952,6 +28892,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28100,6 +29045,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28245,6 +29195,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28390,6 +29345,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28535,6 +29495,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28680,6 +29645,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28825,6 +29795,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28970,6 +29945,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29115,6 +30095,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29260,6 +30245,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29408,6 +30398,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29553,6 +30548,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29698,6 +30698,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29843,6 +30848,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29988,6 +30998,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30133,6 +31148,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30278,6 +31298,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30423,6 +31448,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30568,6 +31598,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30716,6 +31751,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30861,6 +31901,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31006,6 +32051,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31151,6 +32201,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31296,6 +32351,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31441,6 +32501,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31586,6 +32651,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31722,6 +32792,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31867,6 +32942,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32015,6 +33095,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32160,6 +33245,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32305,6 +33395,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32450,6 +33545,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32586,6 +33686,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32731,6 +33836,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32876,6 +33986,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33021,6 +34136,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33166,6 +34286,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33314,6 +34439,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33459,6 +34589,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33604,6 +34739,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33749,6 +34889,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33885,6 +35030,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34030,6 +35180,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34175,6 +35330,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34320,6 +35480,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34465,6 +35630,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34613,6 +35783,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34758,6 +35933,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34903,6 +36083,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35048,6 +36233,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35184,6 +36374,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35329,6 +36524,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35474,6 +36674,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35619,6 +36824,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35764,6 +36974,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35912,6 +37127,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36057,6 +37277,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36202,6 +37427,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36347,6 +37577,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36483,6 +37718,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36628,6 +37868,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36773,6 +38018,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36918,6 +38168,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37063,6 +38318,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37211,6 +38471,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37356,6 +38621,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37501,6 +38771,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37646,6 +38921,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37782,6 +39062,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37918,6 +39203,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38063,6 +39353,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38208,6 +39503,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38353,6 +39653,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38501,6 +39806,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38646,6 +39956,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38791,6 +40106,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38936,6 +40256,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39081,6 +40406,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39226,6 +40556,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39371,6 +40706,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39516,6 +40856,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39661,6 +41006,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39809,6 +41159,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39954,6 +41309,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40099,6 +41459,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40244,6 +41609,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40380,6 +41750,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40525,6 +41900,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40670,6 +42050,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40815,6 +42200,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40960,6 +42350,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41108,6 +42503,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41253,6 +42653,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41398,6 +42803,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41543,6 +42953,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41688,6 +43103,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41833,6 +43253,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41978,6 +43403,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42123,6 +43553,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO288" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42268,6 +43703,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO289" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42416,6 +43856,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO290" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42561,6 +44006,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO291" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42706,6 +44156,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO292" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42851,6 +44306,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO293" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42996,6 +44456,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO294" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43141,6 +44606,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43286,6 +44756,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO296" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43431,6 +44906,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO297" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43576,6 +45056,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO298" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43724,6 +45209,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO299" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43869,6 +45359,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44014,6 +45509,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO301" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44159,6 +45659,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO302" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44304,6 +45809,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO303" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44449,6 +45959,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO304" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44594,6 +46109,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO305" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44739,6 +46259,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO306" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44884,6 +46409,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45032,6 +46562,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO308" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45177,6 +46712,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO309" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45322,6 +46862,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO310" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45467,6 +47012,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO311" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45612,6 +47162,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45757,6 +47312,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO313" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45902,6 +47462,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46047,6 +47612,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO315" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46192,6 +47762,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO316" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46340,6 +47915,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO317" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46485,6 +48065,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46630,6 +48215,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO319" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46775,6 +48365,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO320" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46920,6 +48515,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO321" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47065,6 +48665,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO322" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47210,6 +48815,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO323" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47355,6 +48965,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO324" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47500,6 +49115,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO325" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47648,6 +49268,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO326" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47793,6 +49418,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO327" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47938,6 +49568,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO328" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48083,6 +49718,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO329" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48219,6 +49859,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO330" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48364,6 +50009,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO331" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48509,6 +50159,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO332" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48654,6 +50309,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO333" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48799,6 +50459,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO334" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48947,6 +50612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO335" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49092,6 +50762,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO336" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49237,6 +50912,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO337" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49382,6 +51062,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO338" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49527,6 +51212,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO339" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49672,6 +51362,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO340" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49817,6 +51512,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO341" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49962,6 +51662,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO342" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50107,6 +51812,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO343" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50255,6 +51965,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO344" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50400,6 +52115,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO345" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50545,6 +52265,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO346" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50681,6 +52406,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO347" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50817,6 +52547,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO348" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50962,6 +52697,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO349" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51107,6 +52847,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO350" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51252,6 +52997,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO351" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51397,6 +53147,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO352" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51545,6 +53300,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO353" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51690,6 +53450,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO354" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51835,6 +53600,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO355" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51980,6 +53750,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO356" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52125,6 +53900,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO357" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52270,6 +54050,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO358" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52415,6 +54200,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO359" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52560,6 +54350,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO360" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52705,6 +54500,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO361" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52853,6 +54653,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO362" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52998,6 +54803,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO363" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53143,6 +54953,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO364" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53288,6 +55103,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO365" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53424,6 +55244,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA366" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO366" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53569,6 +55394,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO367" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53714,6 +55544,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO368" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53850,6 +55685,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO369" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53995,6 +55835,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA370" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO370" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54143,6 +55988,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO371" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54288,6 +56138,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO372" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54433,6 +56288,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA373" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO373" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54578,6 +56438,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO374" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54714,6 +56579,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO375" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54859,6 +56729,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO376" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55004,6 +56879,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO377" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55149,6 +57029,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO378" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55294,6 +57179,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA379" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO379" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55442,6 +57332,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO380" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55587,6 +57482,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO381" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55732,6 +57632,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO382" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55877,6 +57782,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO383" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56013,6 +57923,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO384" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56158,6 +58073,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO385" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56303,6 +58223,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO386" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56448,6 +58373,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO387" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56593,6 +58523,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO388" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56741,6 +58676,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO389" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56886,6 +58826,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO390" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57031,6 +58976,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO391" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57176,6 +59126,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA392" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO392" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57312,6 +59267,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA393" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO393" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57457,6 +59417,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA394" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO394" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57602,6 +59567,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA395" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO395" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57747,6 +59717,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA396" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO396" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57892,6 +59867,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA397" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO397" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58040,6 +60020,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA398" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO398" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58185,6 +60170,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA399" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO399" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58330,6 +60320,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA400" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO400" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58475,6 +60470,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA401" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO401" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58620,6 +60620,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA402" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO402" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58765,6 +60770,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA403" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO403" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58910,6 +60920,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA404" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO404" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59055,6 +61070,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA405" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO405" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59200,6 +61220,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA406" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO406" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59348,6 +61373,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA407" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO407" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59493,6 +61523,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO408" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59638,6 +61673,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA409" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO409" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59783,6 +61823,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA410" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO410" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59919,6 +61964,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA411" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO411" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60064,6 +62114,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA412" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO412" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60209,6 +62264,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA413" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO413" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60354,6 +62414,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA414" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO414" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60499,6 +62564,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA415" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO415" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60647,6 +62717,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA416" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO416" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60792,6 +62867,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA417" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO417" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60937,6 +63017,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA418" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO418" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61082,6 +63167,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA419" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO419" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61227,6 +63317,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA420" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO420" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61372,6 +63467,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA421" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO421" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61517,6 +63617,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA422" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO422" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61662,6 +63767,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA423" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO423" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61807,6 +63917,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA424" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO424" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61955,6 +64070,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA425" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO425" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62100,6 +64220,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA426" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO426" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62245,6 +64370,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA427" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO427" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62390,6 +64520,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA428" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO428" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62526,6 +64661,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA429" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO429" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62671,6 +64811,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA430" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO430" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62816,6 +64961,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA431" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO431" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62961,6 +65111,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA432" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO432" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63106,6 +65261,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA433" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO433" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63254,6 +65414,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA434" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO434" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63399,6 +65564,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA435" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO435" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63544,6 +65714,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA436" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO436" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63689,6 +65864,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA437" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO437" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63825,6 +66005,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA438" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO438" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63970,6 +66155,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA439" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO439" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64115,6 +66305,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA440" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO440" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64260,6 +66455,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA441" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO441" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64405,6 +66605,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA442" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO442" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64553,6 +66758,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA443" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO443" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64698,6 +66908,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA444" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO444" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64843,6 +67058,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA445" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO445" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64988,6 +67208,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA446" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO446" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65133,6 +67358,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA447" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO447" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65278,6 +67508,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA448" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO448" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65423,6 +67658,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA449" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO449" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65568,6 +67808,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA450" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO450" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65713,6 +67958,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA451" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO451" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65861,6 +68111,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA452" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO452" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66006,6 +68261,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA453" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO453" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66142,6 +68402,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA454" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO454" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66287,6 +68552,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA455" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO455" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66432,6 +68702,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA456" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO456" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66577,6 +68852,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA457" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO457" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66722,6 +69002,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA458" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO458" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66867,6 +69152,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA459" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO459" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67012,6 +69302,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA460" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO460" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67160,6 +69455,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA461" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO461" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67305,6 +69605,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA462" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO462" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67441,6 +69746,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA463" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO463" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67586,6 +69896,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA464" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO464" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67722,6 +70037,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA465" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO465" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67867,6 +70187,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA466" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO466" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68012,6 +70337,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA467" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO467" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68148,6 +70478,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA468" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO468" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68293,6 +70628,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA469" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO469" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68441,6 +70781,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA470" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO470" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68586,6 +70931,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA471" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO471" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68731,6 +71081,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA472" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO472" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68876,6 +71231,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA473" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO473" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69012,6 +71372,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA474" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO474" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69157,6 +71522,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA475" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO475" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69302,6 +71672,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA476" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO476" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69447,6 +71822,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA477" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO477" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69592,6 +71972,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA478" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO478" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69740,6 +72125,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA479" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO479" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69885,6 +72275,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA480" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO480" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70030,6 +72425,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA481" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO481" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70175,6 +72575,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA482" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO482" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70320,6 +72725,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA483" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO483" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70465,6 +72875,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA484" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO484" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70610,6 +73025,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA485" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO485" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70755,6 +73175,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA486" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO486" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70900,6 +73325,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA487" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO487" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71048,6 +73478,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA488" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO488" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71193,6 +73628,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA489" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO489" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71338,6 +73778,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA490" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO490" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71483,6 +73928,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA491" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO491" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71628,6 +74078,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA492" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO492" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71773,6 +74228,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA493" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO493" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71918,6 +74378,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA494" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO494" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72063,6 +74528,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA495" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO495" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72208,6 +74678,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA496" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO496" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72356,6 +74831,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA497" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO497" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72501,6 +74981,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA498" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO498" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72646,6 +75131,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA499" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO499" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72791,6 +75281,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA500" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO500" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72936,6 +75431,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA501" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO501" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73081,6 +75581,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA502" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO502" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73226,6 +75731,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA503" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO503" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73371,6 +75881,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA504" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO504" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73516,6 +76031,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA505" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO505" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73664,6 +76184,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA506" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO506" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73809,6 +76334,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA507" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO507" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73954,6 +76484,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA508" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO508" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74099,6 +76634,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA509" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO509" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74235,6 +76775,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA510" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO510" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74380,6 +76925,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA511" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO511" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74525,6 +77075,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA512" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO512" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74670,6 +77225,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA513" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO513" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74815,6 +77375,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA514" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO514" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74963,6 +77528,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA515" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO515" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75108,6 +77678,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA516" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO516" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75253,6 +77828,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA517" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO517" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75398,6 +77978,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA518" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO518" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75543,6 +78128,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA519" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO519" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75688,6 +78278,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA520" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO520" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75833,6 +78428,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA521" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO521" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75978,6 +78578,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA522" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO522" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76123,6 +78728,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA523" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO523" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76271,6 +78881,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA524" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO524" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76416,6 +79031,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA525" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO525" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76561,6 +79181,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA526" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO526" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76706,6 +79331,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA527" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO527" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76851,6 +79481,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA528" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO528" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -76996,6 +79631,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA529" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO529" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77141,6 +79781,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA530" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO530" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77286,6 +79931,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA531" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO531" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77431,6 +80081,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA532" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO532" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77579,6 +80234,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA533" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO533" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77724,6 +80384,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA534" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO534" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -77860,6 +80525,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA535" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO535" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78005,6 +80675,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA536" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO536" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78150,6 +80825,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA537" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO537" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78295,6 +80975,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA538" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO538" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78440,6 +81125,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA539" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO539" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78576,6 +81266,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA540" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO540" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -78719,6 +81414,11 @@
       <c r="S541" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA541" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO541" t="inlineStr">
